--- a/evaluation_results.xlsx
+++ b/evaluation_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:N27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,837 +436,1736 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Question_Level</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Question</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Expected_Answer</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Nuclia_Answer</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Position</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Total_Resources_Returned</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Reciprocal_Rank</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>RR_Percentage</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Hit@3</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Hit_Overall</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Match_Info</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Retrieved_Resources</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>retrieved_resources</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Document_20060001.pdf</t>
+          <t>Document_20060008.pdf</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>במסגרת שינוי המבנה/המיזוג לפי סעיף 103, העובדים מחזיקים אופציות בחברה א’ שהוקצו במסלול סעיף 102. מה קובעת החלטת המיסוי לגבי המרת האופציות לאופציות בחברה ג’, והאם נשמר להן הטיפול המיסויי לפי סעיף 102?</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>כן. החלטת המיסוי קובעת כי במסגרת שינוי המבנה, כאשר לעובדים יוקצו אופציות בחברה ג’ במקום האופציות שהחזיקו בחברה א’, האופציות המחליפות ימשיכו להיות מטופלות לצרכי מס כאופציות שהוקצו לפי סעיף 102 לפקודה (בהתאם לכללי מס הכנסה ולתיאומים הנדרשים בהקשר של שינוי מבנה/מיזוג/פיצול). כלומר, עצם ההמרה/החלפה במסגרת המיזוג לא “שוברת” את מסלול 102 של האופציות, בכפוף לעמידה בתנאי ההסדר כפי שנקבע בהחלטה.</t>
-        </is>
+          <t>330 - חוק עידוד</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>מהי הקביעה של רשות המסים בהחלטת מיסוי 8/06 לגבי הגדרת המפעלים של חברה א' וחברה ב' כ"מפעל קשור"?</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>בהחלטה נקבע כי מפעלה של חברה ב' אינו בגדר "מפעל קשור" למפעלה של חברה א', ולהיפך, לפי סעיף 51 לחוק לעידוד השקעות הון. זאת בתנאי שתישמר ההפרדה בין פעילויות המפעלים (מיקום, עובדים וכו').</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>Not enough data to answer this.</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>10</v>
+      </c>
+      <c r="I2" t="n">
         <v>0</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Document_20180019, Document_20090186, Document_20100019, Document_20120024, Document_20180020</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Document_20120009, 5274eb847784991578d99e7c7b14404a, Document_20180035, Document_20160028, Document_20210003</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Document_20060002.pdf</t>
+          <t>Document_20060008.pdf</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>במיזוג לפי סעיף 103 בין חברה א’ לחברה ב’, כאשר יש לחברות זכויות במקרקעין: מה קובעת החלטת המיסוי לגבי מס הרכישה בהעברת הזכויות במקרקעין במסגרת המיזוג, והאם יש דרישת דיווח מיוחדת לאחר מכן?</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">החלטת המיסוי קובעת כי העברת הזכויות במקרקעין במסגרת המיזוג תחויב במס רכישה בשיעור 0.5%. בנוסף, נקבעת דרישת דיווח למנהל מיסוי מקרקעין לאחר תקופת המגבלות/המועדים שנקבעו, לצורך הצהרה/אישור שהחברות עמדו בתנאי סעיף 103 ובתנאי החלטת המיסוי. </t>
-        </is>
+          <t>330 - חוק עידוד</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>באילו תנאים יוכרו מפעלי חברות אחיות העוסקות במוצרים דומים (אורגניים מול הנדסה גנטית) כנפרדים ולא כ"מפעל קשור", והאם הכנסות משירותים ביניהן יוכרו כהכנסה מוטבת?</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ההפרדה תוכר אם קיימת הפרדה מוחלטת בטכנולוגיה, במערכות הנהלת החשבונות, במערכי ההשקעות, בכוח האדם, במשרדים ובהנהלות. עם זאת, הכנסות משירותים שחברה אחת מספקת לשנייה לא ייחשבו כ"הכנסות מוטבות" לצורכי החוק.</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>Not enough data to answer this.</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="n">
         <v>0</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Document_20110054, Document_20100019, Document_20240009, Document_20250023, Document_20120031</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>5274eb847784991578d99e7c7b14404a, 9123c95f23a60d06f190d9b36b05818f, 20260004, Document_20120025, Document_20110055</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Document_20060131.pdf</t>
+          <t>Document_20060008.pdf</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>שני אחים רכשו במשותף קרקע בחלקים שווים. לאחר שנים, בעקבות הפקעה לצורך סלילת כביש נוצר מצב שהקרקע “התפצלה” לשתי חלקות כשכביש עובר ביניהן, וכעת הם מבקשים לבצע פירוק שיתוף/חלוקה בעין כדי שכל אחד יקבל חלק לצורך בניית בית. האם, לפי החלטת המיסוי, ניתן להחיל את סעיף 67 לחוק מיסוי מקרקעין גם כאשר החלקות אינן גובלות בגלל הכביש?</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>כן. החלטת המיסוי קובעת שלצורך יישום סעיף 67 לחוק, בנסיבות שבהן: במקור הייתה חלקה אחת, הפיצול נוצר רק בשל ההפקעה לצורך הקמת כביש, וזכויות האחים לא השתנו לאחר הפיצול, יראו את שתי החלקות כ-“חלקות גובלות ורצופות” לעניין סעיף 67, גם אם בפועל עובר כביש ביניהן—ולכן ניתן להחיל את סעיף 67 על פירוק השיתוף/החלוקה. בנוסף, ההחלטה מבהירה שהיא לא מאשרת כשלעצמה שהחלוקה שתתבצע תהיה בהכרח בהתאם לשווי היחסי של זכויות האחים במקרקעין (ונקבעו גם תנאים/סייגים נוספים במסגרת ההחלטה).</t>
-        </is>
+          <t>330 - חוק עידוד</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>לקוח שלי ביצע פיצול אופקי של חברה לשתי חברות אחיות: אחת ממשיכה בייצור מסורתי והשנייה עוסקת במו"פ והכלאה גנטית של אותם מוצרים. האם הוא יכול להפריד ביניהן לצורכי חוק עידוד והאם השירותים שהן נותנות זו לזו ייהנו מהטבות המס?</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ניתן לבקש הכרה במפעלים כנפרדים (שאינם "מפעל קשור") אם תוכח הפרדה תפעולית, ניהולית וחשבונאית מלאה, וכן שוני מהותי בערך המוצר ובטכנולוגיה. עם זאת, שים לב שמתן שירותים בין החברות (כמו שיווק או ניהול) עלול שלא להיות מוכר כ"הכנסה מוטבת", ולכן לא ניתן יהיה לתבוע בגינו הטבות מס.
+</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>Not enough data to answer this.</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>17</v>
+      </c>
+      <c r="I4" t="n">
         <v>0</v>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Document_20110055, Document_20220001, Document_20170009, Document_20110061, Document_20150007</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Document_20170042, 20260004, 9123c95f23a60d06f190d9b36b05818f, Document_20110070, Document_20240005</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Document_20060132.pdf</t>
+          <t>Document_20060001.pdf</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>נישום מכר דירת מגורים בפטור לפי סעיף 49ב(1) לחוק מיסוי מקרקעין. לאחר מכן רכש קרקע פנויה לבנייה עצמית ומתכוון למכור דירת מגורים נוספת ולבקש פטור לפי סעיף 49ה. האם, לפי החלטת המיסוי, רכישת הקרקע לבנייה עצמית יכולה להיחשב כעמידה בדרישת “דירה אחרת” שבסעיף 49ה(א)(3), ומהם תנאי הזמן והשלמת הבנייה שנקבעו?</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>כן. החלטת המיסוי קובעת כי רכישת קרקע לבנייה עצמית יכולה להיחשב כעמידה בדרישת “דירה אחרת” לצורך סעיף 49ה(א)(3), בכפוף לתנאים שנקבעו, ובין היתר: מועד רכישת הקרקע: רכישת הקרקע צריכה להתבצע בתוך 12 חודשים לפני או אחרי מכירת “הדירה השנייה”. הצהרה והתחייבות לבנייה: עד מועד הדיווח/ההצהרה שנקבע בהחלטה, המבקש ימסור לרשויות הצהרה שהקרקע מיועדת לבניית דירת מגורים, וכן התחייבות לסיים את הבנייה בתוך תקופה שלא תעלה על 3 שנים ממועד מכירת הדירה השנייה. הוכחת סיום הבנייה: כחצי שנה לפני תום המועד שנקבע לסיום הבנייה, המבקש יידרש להוכיח את סיום הבנייה; אם הבנייה לא הסתיימה ולא צפויה להסתיים במועד—הפטור עלול להתבטל (עם אפשרות לשיקול דעת במקרים של עיכובים מוצדקים/שאינם בשליטת המבקש).</t>
-        </is>
+          <t>310 - מיזוגים פיצולים</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>לפי החלטת מיסוי 1/06, מכוח אילו סעיפים בפקודת מס הכנסה ניתן האישור לביצוע המיזוג?</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>האישור לביצוע המיזוג ניתן לפי סעיפים 103כ ו-103ט(ד) לפקודת מס הכנסה, ובכפוף לתקנות מס הכנסה (הקלה ביחסי גודל בסוגי מיזוגים מסוימים), התשס"ג-2003.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>Not enough data to answer this.</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>14</v>
+      </c>
+      <c r="I5" t="n">
         <v>0</v>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Document_20140032, Document_20111000, Document_20140050, Document_20180022, Document_20120012</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Document_20110038, Document_20170038, Document_20100014, Document_20150067, Document_20100019</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Document_20070029.pdf</t>
+          <t>Document_20060001.pdf</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>האם חברה תושבת ישראל שמשקיעה בנכס בחו״ל דרך קרן/שותפות שקופה (שאינה “תושבת” במדינת הזרה) ובאמצעות חברה ייעודית במדינת אמנה—זכאית לזיכוי מס זר (לרבות זיכוי עקיף מכוח אמנה) בישראל בגין המס ששולם בחו״ל?</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>כן. החלטת המיסוי קובעת שהאמנה תחול על החברה הישראלית ביחס להכנסה מהמדינה הזרה גם כאשר ההחזקה היא באמצעות הקרן/השותפות השקופה ובאמצעות החברה הייעודית, ולכן ניתן לדרוש בישראל זיכוי מס זר/זיכוי עקיף בגין המס הזר ששולם (בכפוף להוראות האמנה והדין בישראל ולתנאי ההחלטה). בנוסף נדרש לצרף לדוח פרטים מלאים על ההשקעה, דוחות/מסים ששולמו וחלקה של החברה.</t>
-        </is>
+          <t>310 - מיזוגים פיצולים</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>כיצד נקבע "יום הרכישה" לחישוב רווח ההון הריאלי במניות החברה הקולטת (חברה ג') שהוקצו במסגרת המיזוג המתואר בהחלטה 1/06?</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>נקבע כי מועד הרכישה של מניות חברה ג' יהיה מועד המיזוג. עם זאת, לעניין חישוב רווח ההון הריאלי עד ל"מועד הקובע", יראו את יום רכישת מניות חברה ג' כיום רכישת מניות חברה א' או חברה ב' (המקוריות), לפי העניין.</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>Not enough data to answer this.</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>14</v>
+      </c>
+      <c r="I6" t="n">
         <v>0</v>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Document_20110055, Document_20111000, Document_20110025, Document_20150033, Document_20160038</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Document_20110009, 20260003, Document_20170038, 98cff6b322077ec8227a113b9750de01, Document_20180021</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Document_20070030.pdf</t>
+          <t>Document_20060001.pdf</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>האם לפי החלטת המיסוי, פעילות של חברה תושבת חוץ הכוללת מחסן בישראל לצורכי אחסון/לוגיסטיקה בלבד של חלקים שיוצאו לחו״ל—יוצרת לה “מוסד קבע” בישראל?</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>לא. החלטת המיסוי קובעת כי בנסיבות המתוארות—כאשר הפעילות בישראל מתמצה באחסון/טיפול לוגיסטי מסייע (באמצעות מחסן בישראל) והחברה אינה מנהלת פעילות עסקית מהותית בישראל, אין לה מוסד קבע בישראל. בנוסף נקבע שאין בישראל אדם/סוכן תלוי שמוסמך להתקשר או לחתום בשם החברה, ולכן גם מטעם זה לא נוצר מוסד קבע.</t>
-        </is>
+          <t>310 - מיזוגים פיצולים</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Not enough data to answer this.</t>
+          <t>אני בודק תיק של חברה פרטית שהתמזגה לתוך חברה חדשה. לעובדים היו אופציות במסלול רווח הון (102). האם המיזוג קוטע את רצף המס שלהם ומה קורה אם הם מקבלים אופציות בחברה החדשה במקום הישנות?</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
+          <t>לפי עקרונות החלטת המיסוי 1/06, ניתן לקבל אישור לרצף מס לפי סעיף 102 לפקודה גם בעת מיזוג. במקרה כזה, החלפת האופציות של החברה המתמזגת באופציות של החברה הקולטת לא תיחשב כאירוע מס, בתנאי שנשמרים תנאי המסלול המקורי וההקצאה החדשה באה בנעלי הקודמת.</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>על פי המסמכים שסופקו, במקרה של מיזוג חברה פרטית (החברה המעבירה) לתוך חברה אחרת (החברה הקולטת), ניתן לשמור על רציפות המס עבור בעלי האופציות (מסלול 102), בתנאים מסוימים.
+באחד המסמכים (העוסק במיזוג של חברה פרטית לחברה ציבורית שהינה "שלד בורסאי"), מפורט כי:
+1.  **החלפת הזכויות:** במסגרת המיזוג, הוקצו לבעלי הזכויות בחברה המעבירה (כולל בעלי אופציות) זכויות חדשות בחברה הקולטת, וזאת תוך שמירה על **רציפות מס**.
+2.  **אירוע המס:** החלפת האופציות של החברה המעבירה באופציות חדשות של החברה הישראלית (הקולטת) לא תיחשב כאירוע מס. אירוע המס יידחה למועד המכירה בפועל של הזכויות החדשות או בעת המרתן למניות, לפי המוקדם.
+לסיכום, על בסיס המידע הקיים, המיזוג אינו קוטע בהכרח את רצף המס, וניתן להחליף את האופציות הישנות בחדשות בחברה המתמזגת מבלי שזה ייחשב כאירוע מס במועד המיזוג, בכפוף לעמידה בתנאים שנקבעו בהחלטת המיסוי הספציפית.</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>11</v>
+      </c>
+      <c r="I7" t="n">
         <v>0</v>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Document_20111002, Document_20120009, Document_20260005, Document_20111006, Document_20140035</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Document_20180019, Document_20170006, Document_20100019, Document_20120024, 117ed1ae318b7eb4fc85d5e2d566d01b</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Document_20110024.pdf</t>
+          <t>Document_20060014.pdf</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>בהסדר חוב לפי סעיף 350 לחוק החברות שבו איגרות חוב מקוריות נפדות/מוחלפות בתמורה למזומן + מניות החברה + איגרות חוב חדשות להמרה — האם מדובר באירוע מס, ואיך נקבע ניכוי המס במקור (ריבית/דמי ניכיון מול קרן)?</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>כן. ההחלטה קובעת שפדיון/החלפת איגרות החוב המקוריות בתמורה למזומן, מניות ואיגרות חוב חדשות היא אירוע מס. התקבול במזומן מיוחס תחילה לריבית שנצברה עד יום ההסדר ואז לדמי הניכיון, ועל רכיבים אלה מנכים מס במקור לפי תקנות ניכוי מריבית/דיבידנד/רווחים. יתרת התמורה (מזומן אם נותר, המניות ואיגרות החוב החדשות) מיוחסת לקרן; ועל רווח ההון בפדיון/החלפה מנכים מס במקור לפי תקנות ניכוי מתמורה במכירת נייר ערך.</t>
-        </is>
+          <t>320 - שוק ההון</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>בהתבסס על המידע הקיים, להלן התשובה לשאלתך:
-**האם מדובר באירוע מס?**
-כן. פדיון/החלפת איגרות החוב המקוריות בתמורה למזומן, מניות החברה ואיגרות חוב חדשות הינה אירוע מס לכל דבר ועניין, הן במישור מחזיקי איגרות החוב והן במישור החברה.
-**כיצד נקבע ניכוי המס במקור (ריבית/דמי ניכיון מול קרן)?**
-ניכוי המס במקור מתבצע באופן הבא, על פי סדר הקדימות:
-1.  **ריבית ודמי ניכיון (מהתקבול במזומן):**
-    *   התקבול במזומן שמועבר למחזיקי איגרות החוב ייחשב תחילה (ייוחס) כתשלום בגין הריבית שנצברה עד ליום ביצוע ההסדר.
-    *   לאחר מכן, הסכום הנותר מהמזומן ייוחס לתשלום דמי ניכיון.
-    *   ניכוי המס במקור מחלק זה של התמורה (שסווג כריבית או דמי ניכיון) יבוצע בהתאם לתקנות מס הכנסה (ניכוי מריבית, מדיבידנד ומרווחים מסוימים).
-2.  **קרן (מהתמורה הנותרת):**
-    *   יתרת התקבול במזומן (ככל שנותרה לאחר תשלום הריבית ודמי הניכיון), בצירוף שווי מניות החברה החדשות ושווי איגרות החוב החדשות, ייוחסו לתמורה בגין פדיון/החלפה של קרן איגרות החוב המקוריות.
-    *   ניכוי המס במקור מהרווח המחושב בגין פדיון/החלפת הקרן יבוצע בהתאם לתקנות מס הכנסה (ניכוי מתמורה, מתשלום או מרווח הון במכירת נייר ערך).</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>4</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.25</v>
+          <t>לפי החלטת מיסוי 14/06, כיצד יירשם השותף הכללי במע"מ בנוגע לחלקם של השותפים המוגבלים תושבי ישראל?</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>נקבע כי השותף הכללי יירשם כ"מוסד כספי" כהגדרתו בחוק מע"מ, אך זאת רק לגבי חלקם של השותפים המוגבלים תושבי ישראל בקרן.</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Not enough data to answer this.</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>4th match</t>
-        </is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>9</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Document_20200013, Document_20110025, Document_20260005, Document_20110024, Document_20120003</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Document_20250016, Document_20180041, Document_20200013, Document_20170038, Document_20111000</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Document_20110025.pdf</t>
+          <t>Document_20060014.pdf</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>בהסדר חוב לפי סעיף 350 שבו מחזיקי אג״ח מקבלים מזומן + מניות + אג״ח חדשות להמרה — איך נקבע ניכוי המס במקור: מה נחשב קודם ריבית/דמי ניכיון ומה נחשב קרן?</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>התקבול במזומן מיוחס תחילה לריבית שנצברה עד יום ההסדר ולאחר מכן לדמי הניכיון; על רכיבים אלה מנכים מס במקור לפי תקנות ניכוי מריבית/דיבידנד/רווחים מסוימים. יתרת התמורה (אם נשאר מזומן, וכן המניות והאג״ח החדשות) מיוחסת לקרן, ועל הרווח בפדיון/החלפה מנכים מס במקור לפי תקנות ניכוי מתמורה/מרווח הון במכירת נייר ערך.</t>
-        </is>
+          <t>320 - שוק ההון</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>2</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>בהתאם לטקסט, כך נקבע ניכוי המס במקור בהסדר חוב מהסוג שתיארת:
-1.  **תקבול במזומן (Cash component):** התקבול במזומן שמתקבל ייוחס, לצורכי מס, קודם כל (תחילה) לתשלום הריבית שנצברה עד ליום ביצוע ההסדר, ולאחר מכן לתשלום דמי הניכיון.
-2.  **ניכוי מס במקור על הריבית ודמי הניכיון:** ניכוי המס במקור יבוצע מהתקבול במזומן שסווג כריבית או כדמי ניכיון.
-3.  **פדיון הקרן:** יתרת התקבול במזומן (לאחר ייחוס לריבית ודמי ניכיון), בצירוף שווי המניות החדשות ושווי איגרות החוב החדשות, ייחשבו כתמורה בגין פדיון של קרן איגרות החוב המקוריות.
-4.  **ניכוי מס במקור על פדיון הקרן:** ניכוי המס במקור מהרווח שחושב בגין פדיון/החלפת קרן איגרות החוב יבוצע בהתאם לתקנות מס הכנסה (ניכוי מתמורה, מתשלום או מרווח הון במכירת נייר ערך...).</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>4</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.25</v>
+          <t>מהו הסיווג המיסויי של הכנסות השותפים המוגבלים בקרן הגידור, והאם פעילות הקרן כשלעצמה עלולה לשנות סיווג זה ל"הכנסה מעסק"?</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>הכנסות השותפים המוגבלים יסווגו כהכנסות פסיביות (רווח הון, ריבית או דיבידנד לפי העניין), ונקבע במפורש כי פעילות הקרן כשלעצמה לא תגרום לסיווג הכנסתם כפעילות מעסק.</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>בהתבסס על המידע המצורף, להלן הסיווג המיסויי של הכנסות השותפים המוגבלים והשפעת פעילות הקרן על סיווג זה:
+1.  **השפעת פעילות הקרן על סיווג ההכנסה**: פעילות הקרן כשלעצמה לא תגרום לסיווג הכנסתם של השותף המוגבל הישראלי והשותף המוגבל הזר כ"הכנסה מעסק".
+2.  **בחינה פרטנית של המשקיע**: עם זאת, פקיד השומה עדיין רשאי לבחון את סיווג ההכנסה בידי כל משקיע בנפרד ולקבוע שהיא "הכנסה מעסק" בשל נסיבותיו האחרות של אותו משקיע (לדוגמה, אם הוא סוחר בניירות ערך).
+3.  **אירוע המס**: אירוע המס בידי השותפים המוגבלים (ישראלים וזרים) יתרחש רק במועד פדיון/מכירת היחידה בקרן, או במועד פירוק הקרן. חלוקת רווחים שכבר חויבו במס ברמת הקרן לא תחויב במס נוסף בידי השותפים המוגבלים.
+4.  **הפסדים**: אם במועד אירוע המס (מכירה, פדיון, פירוק) ייצרו הפסדים לשותפים המוגבלים, הם יהיו זכאים לקזזם בהתאם להוראות סעיף 92 לפקודה.</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>4th match</t>
-        </is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>6</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Document_20260005, Document_20120024, Document_20200015, Document_20110025, Document_20180019</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Document_20120003, Document_20250016, Document_20150064, Document_20200013, Document_20120008</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Document_20150043.pdf</t>
+          <t>Document_20060014.pdf</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">האם חברה שמוציאה חשבוניות וגובה תשלומים מלקוחות, אבל חלק מהחובות לא נגבים (חובות אבודים), יכולה להפחית/לקזז מע״מ עסקאות בגין הסכומים שלא נגבו? </t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>לא. לפי ההחלטה, מע״מ עסקאות מחושב לפי “מחיר העסקה” שנקבע בעסקה/בחשבונית, והעובדה שחלק מהחוב לא נגבה אינה כשלעצמה מאפשרת להפחית מע״מ עסקאות. הפחתה תיתכן רק במקרים של ביטול עסקה/הקטנת תמורה כדין ובכפוף לתנאים והמסמכים שנקבעו (למשל זיכוי/תיקון מתאים).</t>
-        </is>
+          <t>320 - שוק ההון</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>3</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Not enough data to answer this.</t>
+          <t>קבוצת יזמים מקימה קרן גידור שתשקיע בניירות ערך עבור משקיעים ישראלים וזרים. הם חוששים שרשות המסים תראה בזה עסק ותחייב אותם במס שולי גבוה. האם יש דרך להבטיח למשקיעים שהכנסתם תישאר הונית, ומה קורה אם נוצרים לקרן הפסדים?</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
+          <t>לפי החלטת מיסוי 14/06, ניתן לקבל אישור שפעילות הקרן לא תהפוך את הכנסת השותפים המוגבלים לעסקית. לגבי הפסדים, נקבע כי אם במועד אירוע המס ייווצרו לשותפים הפסדים מהחזקתם בקרן, הם יסווגו כהפסדי הון שניתן לקזזם לפי סעיף 92 לפקודה.</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>על פי המידע המצורף, ניתן לענות על השאלות כדלקמן:
+*   **הבטחת סיווג ההכנסה כהונית:** פעילות הקרן כשלעצמה לא תגרום לסיווג הכנסתם של השותפים המוגבלים (הישראלים והזרים) מהקרן כפעילות מעסק. עם זאת, מצוין במפורש כי החלטה זו אינה גורעת מאפשרותו של פקיד השומה לבחון את סיווג ההכנסה בידי המשקיעים כהכנסה מעסק בשל נסיבותיהם האחרות (לדוגמא, אצל מי שסוחר בניירות ערך).
+*   **הפסדים בקרן:** במידה וייווצרו הפסדים לשותפים המוגבלים, הישראלים או הזרים, במועד אירוע המס, הם יהיו זכאים לקזזם בהתאם להוראות סעיף 50.2 לפקודה.</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>14</v>
+      </c>
+      <c r="I10" t="n">
         <v>0</v>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Not found</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Document_20180023, Document_20170011, Document_20140019, Document_20150004, Document_20111012</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Document_20240020, Document_20180012, Document_20200013, a7ab9b706cf566e4fc29c2906e3cf1c5, Document_20150046</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Document_20150044.pdf</t>
+          <t>Document_20060018.pdf</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>במפעל תעשייתי מבוזר (שני אתרים: אז״פ א׳ ולא אז״פ א׳) שמייצר מוצרי פלסטיק כקבלן משנה—האם התבניות נחשבות “רכיב במוצר אחר”, ומה תנאי הסף לקבלת ההטבות?</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>ההחלטה קובעת שהמפעל הוא “מפעל תעשייתי”, אבל התבניות אינן “רכיב במוצר אחר”. לעניין ההטבות: בדיקת שיעורי המכירות/השווקים נעשית על כל ההכנסה המועדפת של החברה, והזכאות לכל אתר מותנית בעמידה בתנאי תקנה רלוונטית (לאז״פ א׳ – תקנה 2(א)(1); לאזור שאינו אז״פ א׳ – תקנה 2(א)(3), כולל תנאי מינימום מכירות). בנוסף יש להמציא טופסי 902/אישורי לקוחות כנדרש; ללא האישורים המכירות ייחשבו מכירות בישראל.</t>
-        </is>
+          <t>200 - מיסוי בינלאומי</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>על פי החלטת מיסוי 7587/15, במקרה של מפעל תעשייתי מבוזר (עם אתר באזור פיתוח א' ואתר שאינו באזור פיתוח א') המייצר תבניות ומוצרי פלסטיק כקבלן משנה:
-*   **האם התבניות נחשבות "רכיב במוצר אחר"?** לא. החלטת המיסוי קובעת במפורש כי "תבניות המיוצרות על ידי החברה אינן מהוות רכיב במוצר אחר".
-*   **מה תנאי הסף לקבלת ההטבות?** החברה תוכל לתבוע הטבות מס על הכנסתה המועדפת בתנאי שתעמוד בתנאי "מפעל בר תחרות" לגבי מכירותיה. לשם כך, עליה לעמוד בתנאים הקבועים בתקנות הנוגעים למפעל הממוקם באזור שאינו אזור פיתוח א', הכוללים:
-    1.  שיעור מכירות של 50% או יותר בשוק מסוים.
-    2.  סכום מכירות שלא יפחת מ-15 מיליון שקלים חדשים.</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1</v>
+          <t>לפי החלטת מיסוי 18/06, מהו הסיווג המיסויי של כספי המענק שתקבל המבקשת מקרן מחקר למימון הפוסט-דוקטורט?</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>כספי המענק ייחשבו כהכנסת עבודה החייבת במס בידי המבקשת לפי סעיף 2(2) לפקודת מס הכנסה.</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Not enough data to answer this.</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1st match</t>
-        </is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Document_20150044, Document_20110070, Document_20250002, Document_20090195, Document_20120034</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Document_20150046, Document_20110068, Document_20160010, Document_20250005, Document_20170051</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Document_20170005.pdf</t>
+          <t>Document_20060018.pdf</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>בתמחור מחדש של אופציות במסלול 102 הוני – גם הורדה וגם העלאה של מחיר המימוש – מתי חל המס, והאם מועד התמחור מחדש נחשב “מועד הקצאה” חדש?</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">המס על שווי ההטבה מהאופציות המתומחרות יחושב וינוכה רק במועד המימוש. בנוסף, מועד התמחור מחדש נחשב כמועד הקצאה חדש לכל דבר ועניין (כולל ספירת תקופת החסימה/“תום התקופה” וחישוב רכיב פירותי במקרים הרלוונטיים). </t>
-        </is>
+          <t>200 - מיסוי בינלאומי</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>2</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>בהתבסס על המידע שנמסר, בתמחור מחדש של אופציות לעובדים במסלול 102 הוני, אשר כולל הן הורדה והן העלאה של מחיר המימוש, חלים התנאים הבאים:
-*   **מועד תשלום המס**: המס בגין שווי ההטבה הנובע מהאופציות המתומחרות יחול רק ב"מועד המימוש", כהגדרתו בסעיף 102 לפקודה.
-*   **מועד הקצאה חדש**: כן, "מועד התמחור מחדש" ייחשב כ"מועד ההקצאה החדש" לכל דבר ועניין, לרבות לעניין חישוב "תום התקופה" וחישוב שווי ההטבה.</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>7</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.1428571428571428</v>
+          <t>כיצד מחושב "הסכום הפטור" מניכוי מס במקור עבור חוקרת המבצעת פוסט-דוקטורט בחו"ל, ואילו ימים אינם נכללים במניין הימים לצורך זה?</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>הסכום הפטור שווה ל-$100 ארה"ב כפול מספר הימים שבהם עסקה החוקרת בפוסט-דוקטורט באוניברסיטה בחו"ל. במניין הימים לא יילקחו בחשבון ימי חופשה שבהם שהתה מחוץ למדינת היעד (במקרה זה, ניו יורק).</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Not enough data to answer this.</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>14.3%</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>7th match</t>
-        </is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>5</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Document_20180020, Document_20100019, Document_20170006, Document_20120024, Document_20180019</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Document_20260005, Document_20140035, Document_20200013, Document_20170006, Document_20150029</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Document_20170006.pdf</t>
+          <t>Document_20060018.pdf</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>לעובד שקיבל אופציות/RSU במסלול 102 הוני ועשה רילוקיישן (יציאה מישראל או חזרה לישראל) – איך נקבע החלק החייב במס בישראל, ומה הכלל לגבי זיכוי מסי חוץ?</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">החלק החייב בישראל נקבע יחסית לתקופת ההבשלה/הימים בישראל (“הרווח הישראלי” = שווי ההכנסה × ימי ישראל / סך ימי ההבשלה). בעת מימוש ינוכה מס בישראל על הרווח הישראלי; על יתרת הרווח ניתן זיכוי מסי חוץ רק בגין יתרת הרווח (אין עודף זיכוי). לגבי עובדים שחזרו לישראל – ההכנסה ממוסה לפי סעיף 3(ט), ומועד “המימוש” הוא מועד המרת האופציות למניות. </t>
-        </is>
+          <t>200 - מיסוי בינלאומי</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>3</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>על פי המידע המצוין בהקשר, אלו הכללים לגבי עובדי רילוקיישן (הן היוצאים מישראל והן השבים אליה) שקיבלו אופציות, כולל במסלול 102 הוני:
-**קביעת החלק החייב במס בישראל (הרווח הישראלי):**
-1.  **עובדים היוצאים מישראל:**
-    *   החלק מההכנסה החייב במס בישראל ("הרווח הישראלי") נקבע לפי נוסחה יחסית: שווי ההכנסה הכוללת ממימוש האופציות מוכפל ביחס שבין מספר הימים מיום הקצאת האופציות (או מיום תחילת תקופת ההבשלה, המוקדם מביניהם) ועד ליום עזיבת העובד את ישראל, לבין סך כל מספר הימים מיום ההקצאה (או תחילת ההבשלה, המוקדם) ועד לתום תקופת ההבשלה של האופציות.
-2.  **עובדים השבים לישראל:**
-    *   לגבי עובדים השבים לישראל לאחר שהיו מועסקים בחברות בת מחוץ לישראל, יחולו הוראות סעיף 3(ט) לפקודה. חלק ההכנסה שיחויב במס במקור בישראל ייקבע בהתאם לאותה נוסחה של חישוב הרווח הישראלי המוזכרת בסעיף הקודם, בשינויים המחויבים.
-**הכלל לגבי זיכוי מסי חוץ:**
-1.  **בגין "הרווח הישראלי":**
-    *   לא יינתנו כל הקלה, זיכוי, ניכוי או קיזוז בגין הרווח הישראלי, לרבות זיכוי בגין מסי חוץ. כלומר, על החלק הישראלי של הרווח אין אפשרות לקבל זיכוי על מסים ששולמו בחו"ל.
-2.  **בגין "יתרת הרווח" (החלק הלא-ישראלי):**
-    *   החברה או הנאמן ינכו מס מיתרת הרווח (סך הרווח בניכוי הרווח הישראלי).
-    *   מסכום יתרת הרווח יזוכה מס החוץ ששולם **בגין יתרת רווח זו בלבד**.
-    *   הזיכוי מוגבל: לא יינתן עודף זיכוי בגין מיסי חוץ החלים על יתרת הרווח. כלומר, אם מס החוץ ששולם גבוה מהמס הישראלי על אותו רכיב הכנסה, ההפרש לא יוחזר ולא יועבר לקיזוז כנגד הכנסות אחרות.</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>5</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.2</v>
+          <t>חוקרת ישראלית יוצאת לשנה של פוסט-דוקטורט בלונדון ומקבלת מלגה מהמוסד האקדמי בו עבדה בארץ. היא טוענת שהמלגה צריכה להיות פטורה ממס כמו מלגות סטודנטים רגילות. האם זה נכון, וכיצד יחושב המס על הסכומים שמעבר לתקרה?</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>לפי החלטת מיסוי 18/06, מענק כזה אינו פטור לחלוטין אלא מסווג כהכנסת עבודה. ניתן לקבל פטור מניכוי מס במקור רק על תקרה של $100 ליום שהייה ועבודה בפועל. על כל סכום העולה על תקרה זו, יש לנכות מס במקור בשיעור של 35% (לפי תקנה 6(ז) לתקנות הניכויים).</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Not enough data to answer this.</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>5th match</t>
-        </is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>13</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Document_20180019, Document_20120024, Document_20150005, Document_20140035, Document_20170006</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>73a4c993f89e0db4d331e657f2cc2d57, Document_20180030, Document_20260005, Document_20160010, a7ab9b706cf566e4fc29c2906e3cf1c5</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Document_20250022.pdf</t>
+          <t>Document_20060023.pdf</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">בחברה שמפתחת תוכנה ומוכרת שימוש ושירות מבוסס תוכנה דרך חברות הפצה בחו״ל: מתי כל ההכנסה הטכנולוגית מיוחסת לתוכנות בלבד, ללא ייחוס לנכס שיווקי לא מוחשי? </t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">כל ההכנסה הטכנולוגית מיוחסת לתוכנות בלבד (בלי נכס שיווקי לא מוחשי) אם מתקיימים יחד: לקוחות הקצה הם עסקים אחרים; ההתקשרות מבוססת קריטריונים טכניים; התוכנות מוטמעות בפלטפורמת הקבוצה ומוצעות כחלק מפתרון כולל; פעילות השיווק שולית והוצאות השיווק זניחות. </t>
-        </is>
+          <t>400 - מסמ"ק</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>בהתבסס על החלטת מיסוי 21/2302, נקבע כי אין לחברה נכס לא מוחשי המשמש לשיווק, וכלל ההכנסה הטכנולוגית מיוחסת לתוכנות, בהתקיים כל התנאים הבאים:
-1.  לקוחות הקצה של החברה הינם עסקים אחרים.
-2.  ההתקשרות של לקוחות הקצה לצורך קבלת זכות שימוש מתבססת על פונקציות טכנולוגיות, פתרונות טכנולוגיים, מפרט טכנולוגי של התוכנות, כגון: קריטריון טכני ועלות.</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>3</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.3333333333333333</v>
+          <t>לפי החלטת מיסוי 23/06, האם הסכם מוקדם עם החוכרים על גובה הפיצוי שולל את הזכאות לזיכוי לפי סעיף 48ג לחוק?</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>לא. נקבע כי אין בעובדה שהחברה הגיעה להסכם מוקדם עם החוכרים בדבר גובה הפיצוי כדי לשלול את ההטבה (הזיכוי מהמס) הקבועה בסעיף 48ג לחוק, ובלבד שמדובר בהליך המוגדר כ"הפקעה".</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Not enough data to answer this.</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>3rd match</t>
-        </is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Document_20110068, Document_20260005, Document_20250022, Document_20111006, Document_20180035</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Document_20180017, Document_20220001, Document_20180036, Document_20170006, Document_20180022</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Document_20250023.pdf</t>
+          <t>Document_20060023.pdf</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">במיזוג סטטוטורי של קרן להשקעה במקרקעין לתוך שלד בורסאי, מה נקבע לגבי הפסדים שהיו לשלד במועד המיזוג? </t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">נקבע כי כל ההפסדים שהיו לחברה הקולטת (השלד הבורסאי) במועד המיזוג יימחקו ולא יהיו ניתנים לקיזוז או להעברה לשנים הבאות בשום דרך. </t>
-        </is>
+          <t>400 - מסמ"ק</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>2</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>על פי המסמכים המסומנים "1919/25" ו-"7368/15", במיזוג סטטוטורי של חברה (לרבות קרן להשקעה במקרקעין) לתוך חברה קולטת שהיא שלד בורסאי, נקבע כי ההפסדים שהיו לחברה הקולטת (השלד הבורסאי) טרם ביצוע המיזוג, מכל סוג שהוא, יימחקו, ולא יהיו ניתנים לקיזוז או להעברה בדרך כלשהי.</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>9</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0.1111111111111111</v>
+          <t>כיצד נקבע "יום המכירה" במקרה של הפקעה מכוח הסכם שבו החברה תופסת חזקה לפני השלמת הליכי ההפקעה הרשמיים, לפי החלטה 23/06?</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>יום המכירה נקבע בהתאם לסעיף 19 לחוק מיסוי מקרקעין, קרי: המועד שבו הועמדו הפיצויים לרשות הזכאי או המועד שבו תפסה המדינה חזקה במקרקעין, לפי המוקדם מביניהם.</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Not enough data to answer this.</t>
+        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>11.1%</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>9th match</t>
-        </is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>13</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Document_20250020, Document_20240004, Document_20250005, Document_20110010, Document_20110063</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Document_20250005, Document_20120022, Document_20180021, Document_20110061, Document_20190008</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Document_20060023.pdf</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>400 - מסמ"ק</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>לקוח שלי מחזיק בקרקע חקלאית ותיקה (לפני 1961) שהמדינה רוצה להפקיע לצורך סלילת כביש. המדינה מציעה לו לחתום על הסכם פיצויים מראש כדי לחסוך זמן. האם חתימה על הסכם כזה תפגע לו בהנחת המס של ה-50% המגיעה לו בהפקעה?</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>לפי החלטת מיסוי 23/06, חתימה על הסכם פיצויים מרצון מול המדינה אינה שוללת את הזיכוי של 50% מהמס לפי סעיף 48ג, בתנאי שהמקרקעין אכן מיועדים להפקעה והתהליך יושלם כדין. מכיוון שהקרקע נרכשה לפני 1961, הוא עשוי להיות זכאי גם לשיעור מס היסטורי מוגבל, וההסכם יסווג כ"הפקעה" לצורכי המס.</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Not enough data to answer this.</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>11</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Document_20170053, Document_20180018, Document_20110070, Document_20180022, Document_20180019</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>Document_20060030.pdf</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>370 - אופציות</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>לפי החלטת מיסוי 30/06, מהם התנאים הכלכליים שחייבים להתקיים בהחלפת האופציות הישנות באופציות של החברה הרוכשת?</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>נקבע כי יש להתאים את מחיר המימוש ויחס ההמרה כך שהשווי הכלכלי של האופציות ערב ההחלפה יהיה זהה לשווי הכלכלי שלהן מיד לאחר ההחלפה.</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Not enough data to answer this.</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>11</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Document_20120024, Document_20180019, Document_20120022, 117ed1ae318b7eb4fc85d5e2d566d01b, a7ab9b706cf566e4fc29c2906e3cf1c5</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Document_20060030.pdf</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>370 - אופציות</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>האם החלפת אופציות 102 שטרם הבשילו (Unvested) במועד עסקת רכישה נחשבת לאירוע מס, וכיצד היא משפיעה על תקופת החסימה המקורית?</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>החלפת אופציות (בשלות או שאינן בשלות) לא תיחשב כאירוע מס וייקבע להן "רצף מס" (כניסה לנעליים). תקופת החסימה המקורית לפי סעיף 102 ממשיכה להימנות ממועד ההקצאה המקורי בחברה הנרכשת.</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Not enough data to answer this.</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>8</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Document_20180019, Document_20100019, Document_20120024, 117ed1ae318b7eb4fc85d5e2d566d01b, Document_20170005</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Document_20060030.pdf</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>370 - אופציות</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>3</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>חברת סטארט-אפ ישראלית נרכשת על ידי ענקית טכנולוגיה אמריקאית. העובדים מחזיקים באופציות במסלול הוני שאמורות להיות מוחלפות באופציות של החברה האמריקאית. האם הם צריכים לשלם מס במועד ההחלפה, ומה קורה אם חלק מהאופציות ממומשות למניות מיד לאחר הרכישה?</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>לפי החלטת מיסוי 30/06, עצם ההחלפה אינה אירוע מס ומתקיים רצף מס מלא. עם זאת, אם עובד יממש את האופציות למניות וימכור אותן לפני תום תקופת החסימה המקורית (שנתיים ממועד ההקצאה הראשון), הוא יחויב במס לפי מסלול פירותי (הכנסת עבודה) ולא הוני.</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Not enough data to answer this.</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>8</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Document_20100019, Document_20170006, Document_20120022, 117ed1ae318b7eb4fc85d5e2d566d01b, Document_20180019</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Document_20150026.pdf</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>325 - קופות גמל ומיסוי יחיד</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>לפי החלטת מיסוי 6849/15, החל מאיזו שנה התחייבה החברה המנהלת לקלוט תשלומים פטורים מהמעבידים באופן ממוחשב בעת הפקדתם?</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>החברה המנהלת התחייבה ליישם את קליטת התשלומים הפטורים באופן ממוחשב החל משנת 2016.</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>לפי החלטת מיסוי 6849/15, החברה המנהלת התחייבה ליישם את התקנות והוראות הממונה ולקלוט תשלומים פטורים מהמעבידים באופן ממוחשב כבר בעת הפקדתם החל משנת 2016.</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" t="n">
+        <v>15</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>1st match</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Document_20150026, Document_20110012, Document_20120022, Document_20110070, Document_20140035</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Document_20150026.pdf</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>325 - קופות גמל ומיסוי יחיד</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>מהם התנאים שבהם חברה מנהלת של קופת גמל רשאית לנכות מס במקור בעת היוון קצבה מוכרת ללא צורך באישור פרטני מפקיד השומה?</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>התנאים כוללים "צביעה" של סכומים פטורים בדוחות החל משנת 2015 (עבור הפקדות מ-2012), ניהול חשבונות תוך הפרדה לקצבה מוכרת, ועמידה בטבלת מקדמים אחידה לגברים ונשים לצורך חישוב תקרות ההיוון.</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>על פי המסמכים, התנאים שבהם חברה מנהלת של קופת גמל רשאית לנכות מס במקור בעת היוון קצבה מוכרת ללא צורך באישור פרטני מפקיד השומה הם כדלקמן:
+1.  **סימון כספים (צביעה):** החברה המנהלת התחייבה לסמן (לצבוע) כבר בדוחות 2015 את כל הסכומים שהופקדו לאחר 1.1.2012 כתשלומים פטורים. זה כולל הפקדות מעביד מעל התקרות והפקדות עצמאיות מעל התקרות.
+2.  **קליטה ממוחשבת:** החל משנת 2016, החברה המנהלת תיישם מערכת לקלוט באופן ממוחשב תשלומים פטורים מהמעבידים כבר בעת ההפקדה.
+3.  **הפרדה בחשבון:** החל משנת 2015, החברה המנהלת תנהל את חשבונות העמית תוך הפרדה בין סכומים המיועדים לקצבה מוכרת וסכומים המיועדים לקצבה מזכה.
+4.  **גיל העמית:** העמית הינו בן 60 או יותר.
+5.  **קצבה מזערית:** העמית מקבל קצבה מזערית (כהגדרתה בחוק) והציג שלושה תלושי שכר.
+6.  **עמידה בתקרת ההפקדה:** העמית הפקיד סכומים כתשלומים פטורים כך שהסכומים הצבורים לקצבה מוכרת בכל חשבונותיו (כולל בחברות אחרות), בתוספת סכומים שכבר משך כקצבה מוכרת או בהיוון, לא יעלו על התקרה שנקבעה (הסכום הדרוש לקצבה של 4 פעמים השכר הממוצע במשק, בהתאם לגיל).</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>10</v>
+      </c>
+      <c r="H21" t="n">
+        <v>14</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>10.0%</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>10th match</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Document_20120039, Document_20260005, Document_20170003, Document_20150027, Document_20120008</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Document_20150026.pdf</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>325 - קופות גמל ומיסוי יחיד</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>עמית בקופת גמל מעוניין למשוך סכום חד-פעמי (היוון) מהכספים שהפקיד מעבר לתקרת המזכה במיסוי. הקופה טוענת שהוא חייב להביא אישור פקיד שומה כדי שלא ינכו לו 35% מס. האם יש הסדר שמאפשר לקופה לבצע זאת אוטומטית?</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>כן, לפי החלטת מיסוי 6849/15, אם הקופה מיישמת את הסדר הדיווח וההפרדה הממוחשבת של "קצבה מוכרת", היא יכולה לבצע את ניכוי המס במקור (או לתת פטור על החלק המוכר) בעת ההיוון באופן עצמאי, בהסתמך על נתוניה הממוחשבים ועל טבלת מקדמים מאושרת, ללא צורך בהפניית העמית לפקיד השומה.</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Not enough data to answer this.</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" t="n">
+        <v>16</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>1st match</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Document_20150026, 9123c95f23a60d06f190d9b36b05818f, Document_20260005, Document_20150005, Document_20170029</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Document_20250006.pdf</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>500 - מע"מ</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>לפי החלטת מיסוי 6033/25, אילו שלושה סוגי שירותים נוספים פרט לתיקון מוצרים ייהנו ממע"מ בשיעור אפס תחת התנאים המפורטים?</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>השירותים הנוספים הם: שירותי פרסום, שירותי שיווק ושירותי קידום מכירות הניתנים על ידי עוסק ישראלי לתושב חוץ עבור טובין מיובאים.</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Not enough data to answer this.</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>11</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Document_20111004, Document_20190007, Document_20200010, Document_20111008, Document_20111000</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Document_20250006.pdf</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>500 - מע"מ</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>מהם התנאים המצטברים שצריכים להתקיים כדי ששירות תיקונים למוצרים מיובאים יזכה למע"מ בשיעור אפס, למרות שהמוצרים נמצאים פיזית בישראל בעת התיקון?</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>התנאים הם: השירות ניתן לתושב חוץ שאין לו פעילות בישראל, התיקון הוא במסגרת תקופת האחריות, התמורה משולמת רק על ידי תושב החוץ, מחיר המוצר לצרכן הסופי כלל את עלות האחריות (ומע"מ שולם עליו בייבוא), וקיימת הצהרה חתומה של תושב החוץ והעוסק.</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>על פי המידע שסופק, התנאים המצטברים כדי ששירות תיקונים למוצרים מיובאים יזכה למע"מ בשיעור אפס, לאחר תום תקופת האחריות, הם:
+*   השירות ניתן עקב כך שהחברה הזרה מתכננת לפעול בישראל.
+*   החברה הזרה חייבת למנות לצורך כך נציג תושב ישראל.
+*   החברה הזרה חייבת להירשם כעוסק מורשה בישראל.
+ההקשר מציין תנאים אלו באופן ספציפי לגבי "שירותים טכניים וחלפים לאחר תום תקופת האחריות".</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>10</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Document_20160009, Document_20190007, Document_20111006, Document_20111000, Document_20170008</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Document_20250006.pdf</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>500 - מע"מ</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>3</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>חברה ישראלית משמשת כמרכז שירות ותמיכה עבור יצרן אלקטרוניקה בינלאומי. היא מתקנת מכשירים של לקוחות ישראלים שנרכשו בייבוא רשמי. מנהל החשבונות טוען שחייבים לגבות מע"מ כי השירות ניתן על נכס שנמצא בישראל. האם החלטת מיסוי 6033/25 משנה את המצב?</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>כן. החלטה 6033/25 קובעת כי למרות שהנכס נמצא בישראל, ניתן להחיל מע"מ בשיעור אפס לפי סעיף 30(א)(5) לחוק, כיוון שמדובר בשירות לתושב חוץ במסגרת "אחריות יצרן". ההיגיון הוא שהמע"מ על שירות התיקון כבר שולם למעשה בעת ייבוא המכשיר (כחלק ממחיר המוצר), ולכן אין כאן אובדן מס למדינה. יש להקפיד על קבלת הצהרות מתאימות ותשלום ישיר מתושב החוץ.</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>על פי החלטת מיסוי 1/11, ייתכן שהחלטת המיסוי תשנה את המצב, בכפוף לתנאים מסוימים.
+ההחלטה קובעת כי על שירותים הניתנים על ידי חברה ישראלית (כקבלן משנה) לחברה זרה במהלך תקופת האחריות, יחול מע"מ בשיעור אפס, למרות שהשירות ניתן בישראל. זאת בתנאי שמתקיימים מספר תנאים מצטברים, ביניהם שהחברה הזרה אינה רשומה בישראל ושהתשלום עבור השירותים והחלפים בתקופת האחריות כלול בשווי הטובין שייבא הלקוח הישראלי.
+עם זאת, לאחר תום תקופת האחריות, על החברה הזרה לפעול בישראל, למנות נציג ולהירשם כעוסק מורשה, והשירותים ייחשבו כעסקה החייבת במע"מ בשיעור מלא.</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>6</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Document_20111006, Document_20111000, Document_20160024, Document_20150028, Document_20111004</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>SUMMARY</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>14 questions evaluated</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="n">
-        <v>0.1633786848072562</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>16.3%</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>14.3%</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>MRR: 0.16, Hit@3: 2/14</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>24 questions evaluated</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="n">
+        <v>0.08750000000000001</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>8.8%</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>8.3%</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>MRR: 0.09, Hit@3: 2/24, Hit Overall: 3/24</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
